--- a/nr-doc-core-medication/ig/ValueSet-fr-core-vs-availability-time-rule.xlsx
+++ b/nr-doc-core-medication/ig/ValueSet-fr-core-vs-availability-time-rule.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:31:13+00:00</t>
+    <t>2026-10-15T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
